--- a/uch_iznos.xlsx
+++ b/uch_iznos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bddaca42e7ba7ab0/Рабочий стол/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{4D4D386B-23AD-4561-AC23-9293034FF91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17014E22-85D3-424B-B532-B64FDBC1C295}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{4D4D386B-23AD-4561-AC23-9293034FF91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF06092-9B30-42B5-A4CD-0ABDB208794F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5829B126-2AFF-40D5-A8F5-C329927BE3D8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Обрабатывающие производства</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Деятельность профессиональная</t>
+  </si>
+  <si>
+    <t>Регион</t>
   </si>
 </sst>
 </file>
@@ -801,7 +804,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:176" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5"/>
+      <c r="A1" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="B1" s="7" t="s">
         <v>91</v>
       </c>
